--- a/SuppXLS/Scen_FF2Upd.xlsx
+++ b/SuppXLS/Scen_FF2Upd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4ee46c55b5fc2ded/Documents/Git/times-ireland-model/SuppXLS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCDEF030-9EAD-48CD-BFAD-E1BF223A795C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{DCDEF030-9EAD-48CD-BFAD-E1BF223A795C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F820FCE8-411A-4E31-A4CD-2AAD41AA3D4C}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="17280" windowHeight="9960" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="24" r:id="rId1"/>
@@ -430,10 +430,10 @@
     <t>IMPELC*,IMPBIO*</t>
   </si>
   <si>
-    <t>*10</t>
-  </si>
-  <si>
-    <t>*8</t>
+    <t>*2</t>
+  </si>
+  <si>
+    <t>*1.5</t>
   </si>
 </sst>
 </file>
@@ -1141,10 +1141,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
